--- a/data.xlsx
+++ b/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,6 @@
           <t>Data_Slots</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Số Pallet</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -479,23 +469,21 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2,4,6</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -521,12 +509,6 @@
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -551,12 +533,6 @@
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -581,12 +557,6 @@
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -611,12 +581,6 @@
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -641,12 +605,6 @@
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -671,12 +629,6 @@
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" t="n">
-        <v>7</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -701,12 +653,6 @@
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -719,23 +665,21 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>9</v>
+        <v>3</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2,4,6</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -761,12 +705,6 @@
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr"/>
-      <c r="I11" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" t="n">
-        <v>10</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -791,12 +729,6 @@
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" t="n">
-        <v>11</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -821,12 +753,6 @@
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="n">
-        <v>12</v>
-      </c>
-      <c r="J13" t="n">
-        <v>12</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -851,12 +777,6 @@
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="n">
-        <v>13</v>
-      </c>
-      <c r="J14" t="n">
-        <v>13</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -881,12 +801,6 @@
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="n">
-        <v>14</v>
-      </c>
-      <c r="J15" t="n">
-        <v>14</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -911,12 +825,6 @@
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" t="n">
-        <v>15</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -941,12 +849,6 @@
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="n">
-        <v>16</v>
-      </c>
-      <c r="J17" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -959,23 +861,21 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>17</v>
-      </c>
-      <c r="J18" t="n">
-        <v>17</v>
+        <v>2</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1001,12 +901,6 @@
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>18</v>
-      </c>
-      <c r="J19" t="n">
-        <v>18</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1031,12 +925,6 @@
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="n">
-        <v>19</v>
-      </c>
-      <c r="J20" t="n">
-        <v>19</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1061,12 +949,6 @@
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="n">
-        <v>20</v>
-      </c>
-      <c r="J21" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1091,12 +973,6 @@
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="n">
-        <v>21</v>
-      </c>
-      <c r="J22" t="n">
-        <v>21</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1121,12 +997,6 @@
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="n">
-        <v>22</v>
-      </c>
-      <c r="J23" t="n">
-        <v>22</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1151,12 +1021,6 @@
         <v>0</v>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>23</v>
-      </c>
-      <c r="J24" t="n">
-        <v>23</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1181,792 +1045,6 @@
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="n">
-        <v>24</v>
-      </c>
-      <c r="J25" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="n">
-        <v>39</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="n">
-        <v>25</v>
-      </c>
-      <c r="J26" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="n">
-        <v>41</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="n">
-        <v>26</v>
-      </c>
-      <c r="J27" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="n">
-        <v>43</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="n">
-        <v>27</v>
-      </c>
-      <c r="J28" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="n">
-        <v>45</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="n">
-        <v>28</v>
-      </c>
-      <c r="J29" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>41</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>29</v>
-      </c>
-      <c r="J30" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="n">
-        <v>43</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="n">
-        <v>45</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="n">
-        <v>31</v>
-      </c>
-      <c r="J32" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="n">
-        <v>47</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="n">
-        <v>32</v>
-      </c>
-      <c r="J33" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="n">
-        <v>33</v>
-      </c>
-      <c r="J34" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="n">
-        <v>34</v>
-      </c>
-      <c r="J35" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="n">
-        <v>35</v>
-      </c>
-      <c r="J36" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="n">
-        <v>36</v>
-      </c>
-      <c r="J37" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="n">
-        <v>37</v>
-      </c>
-      <c r="J38" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="n">
-        <v>38</v>
-      </c>
-      <c r="J39" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="n">
-        <v>39</v>
-      </c>
-      <c r="J40" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="n">
-        <v>40</v>
-      </c>
-      <c r="J41" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="n">
-        <v>41</v>
-      </c>
-      <c r="J42" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="n">
-        <v>42</v>
-      </c>
-      <c r="J43" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>43</v>
-      </c>
-      <c r="J44" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="n">
-        <v>44</v>
-      </c>
-      <c r="J45" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="n">
-        <v>45</v>
-      </c>
-      <c r="J46" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="n">
-        <v>46</v>
-      </c>
-      <c r="J47" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="n">
-        <v>47</v>
-      </c>
-      <c r="J48" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="n">
-        <v>48</v>
-      </c>
-      <c r="J49" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="n">
-        <v>49</v>
-      </c>
-      <c r="J50" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="n">
-        <v>50</v>
-      </c>
-      <c r="J51" t="n">
-        <v>50</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
